--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Statistical_Validation/tables/exploratory_evidence.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Statistical_Validation/tables/exploratory_evidence.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,22 +537,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65.66197244947071</v>
+        <v>68.50432172022388</v>
       </c>
       <c r="D2" t="n">
         <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001286183419324869</v>
+        <v>0.0006037664252750105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.421868161538557</v>
+        <v>0.1980353874902034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05273352019231962</v>
+        <v>0.02475442343627543</v>
       </c>
       <c r="H2" t="n">
-        <v>0.256245921820174</v>
+        <v>0.247314724520166</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -569,7 +569,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001286183419324869</v>
+        <v>0.0006037664252750105</v>
       </c>
     </row>
     <row r="3">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.48264731607355</v>
+        <v>14.5405572774308</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08576273356357941</v>
+        <v>0.04236106665679771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24982641289577</v>
+        <v>0.2547806941889191</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -627,66 +627,66 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8430715509268312</v>
+        <v>0.8704897822446489</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P3" t="b">
         <v>0</v>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08576273356357941</v>
+        <v>0.04236106665679771</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.86590646617123</v>
+        <v>12.18164420537235</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04755964831037239</v>
+        <v>0.03238184657806457</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2442637225734269</v>
+        <v>0.2332002148424292</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8489401726858951</v>
+        <v>0.8429996990577381</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -723,37 +723,37 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04755964831037239</v>
+        <v>0.03238184657806457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>desktop_category_display</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.18817882088389</v>
+        <v>33.80211705015776</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01007289052385354</v>
+        <v>0.03804560723180549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4129885114779952</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2407705277898641</v>
+        <v>0.2242783302503334</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8655227202133037</v>
+        <v>0.8293622354354354</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01007289052385354</v>
+        <v>0.03804560723180549</v>
       </c>
     </row>
     <row r="6">
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.84472373991052</v>
+        <v>44.35431867020466</v>
       </c>
       <c r="D6" t="n">
         <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01808408902555184</v>
+        <v>0.02562016680233264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3707238250238127</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2393865173206046</v>
+        <v>0.2224917701883998</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8736398889490427</v>
+        <v>0.8312914079845187</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -857,37 +857,37 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01808408902555184</v>
+        <v>0.02562016680233264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>desktop_category_display</t>
+          <t>recommendation_type</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.650420437344</v>
+        <v>32.1841524208596</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03948431736169739</v>
+        <v>0.006076529755922339</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.1673443007117269</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2368206791271404</v>
+        <v>0.2188448856144747</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8414788715893061</v>
+        <v>0.9146708149917904</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03948431736169739</v>
+        <v>0.006076529755922339</v>
       </c>
     </row>
     <row r="8">
@@ -935,26 +935,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>desktop_image_text_ratio</t>
+          <t>mobile_filter_location</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.42810448978032</v>
+        <v>21.4009937203421</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07023543703578852</v>
+        <v>0.091789215403546</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2367915987201632</v>
+        <v>0.2185636641087003</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8304975916476448</v>
+        <v>0.7683149515036278</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07023543703578852</v>
+        <v>0.091789215403546</v>
       </c>
     </row>
     <row r="9">
@@ -1002,26 +1002,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mobile_filter_location</t>
+          <t>desktop_search_visibility</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.82628163872918</v>
+        <v>21.28800831117746</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08225498145138996</v>
+        <v>0.09447644303641907</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2335930309252032</v>
+        <v>0.2179859529753982</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8217800700514118</v>
+        <v>0.7665492064297157</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1058,37 +1058,37 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08225498145138996</v>
+        <v>0.09447644303641907</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.52481747380307</v>
+        <v>21.27011268026897</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06165930323619846</v>
+        <v>0.01928683302746032</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.3953800770629365</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2293994057730215</v>
+        <v>0.2178943094481499</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1096,66 +1096,66 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="b">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7900144901512944</v>
+        <v>0.8389761699752223</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P10" t="b">
         <v>0</v>
       </c>
       <c r="Q10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.06165930323619846</v>
+        <v>0.01928683302746032</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>recommendation_type</t>
+          <t>social_proof_display</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31.39106946323544</v>
+        <v>10.56183481569735</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0.007784440760364039</v>
+        <v>0.03195580725403268</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1595810355874628</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2287322651166477</v>
+        <v>0.2171429213314659</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9269018048245539</v>
+        <v>0.8206912347577575</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1192,37 +1192,37 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.007784440760364039</v>
+        <v>0.03195580725403268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>mobile_price_display</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.2980214084662</v>
+        <v>21.05260853833937</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06721813151455883</v>
+        <v>0.02072969480257041</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.2833058289684623</v>
       </c>
       <c r="H12" t="n">
-        <v>0.226914316521305</v>
+        <v>0.2167773737572234</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1230,66 +1230,66 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="b">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7845862594788657</v>
+        <v>0.8711345115542989</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P12" t="b">
         <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="b">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06721813151455883</v>
+        <v>0.02072969480257041</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mobile_sticky_header</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.04906946603638</v>
+        <v>10.20353848084781</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07385676408238892</v>
+        <v>0.0696692642803356</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6119327087415978</v>
+        <v>0.5148141803841989</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2241547397004621</v>
+        <v>0.2134279997451446</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.759088297650598</v>
+        <v>0.7782906838450014</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1326,37 +1326,37 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.07385676408238892</v>
+        <v>0.0696692642803356</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>desktop_price_display</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40.19126297856479</v>
+        <v>19.62573317382398</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06357757297916758</v>
+        <v>0.03299809885565442</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.6361436320471427</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2241407564973537</v>
+        <v>0.2093022697443647</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1364,66 +1364,66 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="b">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8153011199927468</v>
+        <v>0.7485265190253044</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P14" t="b">
         <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06357757297916758</v>
+        <v>0.03299809885565442</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hero_banner_size</t>
+          <t>mobile_whitespace</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29.7058476100724</v>
+        <v>19.44250377428342</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09806027772742136</v>
+        <v>0.03498911993653327</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4467190429804751</v>
+        <v>0.358638479349466</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2225078560788075</v>
+        <v>0.2083229366266225</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1431,66 +1431,66 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7985741736838935</v>
+        <v>0.8312154939217499</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P15" t="b">
         <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="b">
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09806027772742136</v>
+        <v>0.03498911993653327</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48.45276345166277</v>
+        <v>38.61931088272131</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>0.003290526498034538</v>
+        <v>0.08724306358434311</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5396463456776642</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1349115864194161</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2201198842714187</v>
+        <v>0.2076099936595608</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1498,66 +1498,66 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9240659301618951</v>
+        <v>0.7546135426041427</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P16" t="b">
         <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="b">
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.003290526498034538</v>
+        <v>0.08724306358434311</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Agreeableness_Level</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19.22358129100138</v>
+        <v>45.09188072435776</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03751305597841784</v>
+        <v>0.008163136620084241</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7192283768587451</v>
+        <v>0.1673443007117269</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2192235234355644</v>
+        <v>0.2006504617228805</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7324510745960361</v>
+        <v>0.8884775696395767</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1594,45 +1594,45 @@
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.03751305597841784</v>
+        <v>0.008163136620084241</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mobile_grid_pref</t>
+          <t>desktop_persistent_filters</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.585975882803975</v>
+        <v>8.499351138512278</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02243409391836799</v>
+        <v>0.01426886241579131</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.3953800770629365</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2189289369042381</v>
+        <v>0.1947909953472141</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -1644,62 +1644,62 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7894324882992878</v>
+        <v>0.8084484746312579</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P18" t="b">
         <v>0</v>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="b">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.02243409391836799</v>
+        <v>0.01426886241579131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mobile_price_display</t>
+          <t>mobile_grid_pref</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18.84612192927982</v>
+        <v>8.169479085881928</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0422612621360954</v>
+        <v>0.04263591033019484</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5775705825266372</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2170606017295621</v>
+        <v>0.1909735289935718</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -1711,30 +1711,30 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7709587881797708</v>
+        <v>0.7802804009117931</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P19" t="b">
         <v>0</v>
       </c>
       <c r="Q19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0422612621360954</v>
+        <v>0.04263591033019484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1743,176 +1743,176 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.56380493892523</v>
+        <v>15.50399825550793</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02474531586029017</v>
+        <v>0.05005528995298282</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6314667347914755</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.6361436320471427</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2095459671463831</v>
+        <v>0.1860299410395739</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7902203425447025</v>
+        <v>0.7098953337359075</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="b">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.02474531586029017</v>
+        <v>0.05005528995298282</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>desktop_navigation</t>
+          <t>font_style_pref</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.393373537164944</v>
+        <v>22.92538339147183</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>0.038544379976584</v>
+        <v>0.08573700904176919</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.5858695617854228</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2048581648014663</v>
+        <v>0.1847028799352</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7641638402890324</v>
+        <v>0.7106799690393864</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.038544379976584</v>
+        <v>0.08573700904176919</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>social_proof_display</t>
+          <t>hero_banner_size</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.327633523028096</v>
+        <v>15.24606030978499</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0802875452349027</v>
+        <v>0.01842687334407999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.4043739620417602</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2040543251566614</v>
+        <v>0.1844759730156093</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7481959871679926</v>
+        <v>0.7897910920739846</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1929,45 +1929,45 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0802875452349027</v>
+        <v>0.01842687334407999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>Conscientiousness_Level</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.25633145468555</v>
+        <v>14.89498586621506</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09252597659675929</v>
+        <v>0.06121984757975202</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4584486025236872</v>
+        <v>0.5709540419064413</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2015957058984984</v>
+        <v>0.1823396180442302</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7679303378444348</v>
+        <v>0.7206678689062445</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1996,45 +1996,45 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.09252597659675929</v>
+        <v>0.06121984757975202</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Conscientiousness_Level</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.14305813462319</v>
+        <v>14.64066541203707</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09560977545161779</v>
+        <v>0.06652080313546443</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2008921236299671</v>
+        <v>0.1807762615038186</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7588356505841873</v>
+        <v>0.7640253480660268</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2063,74 +2063,74 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.09560977545161779</v>
+        <v>0.06652080313546443</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Openness_Level</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mobile_product_card</t>
+          <t>background_pref</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.05607182887269</v>
+        <v>29.11906780015476</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04158454723497933</v>
+        <v>0.0854412301871352</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5135785999327165</v>
+        <v>0.5858695617854228</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2003501424311491</v>
+        <v>0.1802746781952113</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7675127603256419</v>
+        <v>0.7045913877147174</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P25" t="b">
         <v>0</v>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="b">
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.04158454723497933</v>
+        <v>0.0854412301871352</v>
       </c>
     </row>
     <row r="26">
@@ -2141,26 +2141,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>social_proof_display</t>
+          <t>checkout_style</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14.95516295459562</v>
+        <v>14.5483034766774</v>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06002317400917948</v>
+        <v>0.06854683953755153</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.5787902541962363</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1933595288225772</v>
+        <v>0.180205137798599</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7551945570894705</v>
+        <v>0.7126773766346298</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2197,37 +2197,37 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.06002317400917948</v>
+        <v>0.06854683953755153</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>recommendation_type</t>
+          <t>social_proof_display</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.83527353993628</v>
+        <v>14.45788677109763</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02157734490210973</v>
+        <v>0.07058417734100443</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4423355704932495</v>
+        <v>0.5787902541962363</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1925829272023891</v>
+        <v>0.1796442837539947</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2235,19 +2235,19 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.785572985639454</v>
+        <v>0.7111668163418423</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2264,13 +2264,13 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.02157734490210973</v>
+        <v>0.07058417734100443</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Agreeableness_Level</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2279,22 +2279,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14.16520058162846</v>
+        <v>14.26104427429195</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07755985176116741</v>
+        <v>0.07521004644075296</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7192283768587451</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1881834250248176</v>
+        <v>0.1784171743758398</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6751047520576057</v>
+        <v>0.7576289059283144</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2331,37 +2331,37 @@
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.07755985176116741</v>
+        <v>0.07521004644075296</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Conscientiousness_Level</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>desktop_grid_pref</t>
+          <t>urgency_pref</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14.15657455242141</v>
+        <v>13.83575937100729</v>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07777454261451397</v>
+        <v>0.08614801146160327</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1881261182851906</v>
+        <v>0.1757367106018013</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7474560610402403</v>
+        <v>0.7499815424726431</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2398,37 +2398,37 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.07777454261451397</v>
+        <v>0.08614801146160327</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Openness_Level</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mobile_category_display</t>
+          <t>mobile_navigation</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13.74280265772146</v>
+        <v>13.83226302974856</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00816282292854476</v>
+        <v>0.0315670455689609</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3346757400703352</v>
+        <v>0.4314162894424657</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1853564313540365</v>
+        <v>0.1757145045805111</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.813144112889837</v>
+        <v>0.7645925377321275</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2465,37 +2465,37 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00816282292854476</v>
+        <v>0.0315670455689609</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Conscientiousness_Level</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>desktop_navigation</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.70033860152438</v>
+        <v>6.894466050220771</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0899181608411789</v>
+        <v>0.0753386605440291</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.5148141803841989</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1850698422320907</v>
+        <v>0.1754390671875237</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.738891962628432</v>
+        <v>0.723132854065804</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0899181608411789</v>
+        <v>0.0753386605440291</v>
       </c>
     </row>
     <row r="32">
@@ -2543,26 +2543,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>background_pref</t>
+          <t>mobile_whitespace</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.61626700847079</v>
+        <v>13.70803696933256</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>0.09233202863200983</v>
+        <v>0.008287613941412596</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.3397921715979164</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1845011314902349</v>
+        <v>0.1749236885231554</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2570,19 +2570,19 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.7372435000424096</v>
+        <v>0.7997706793257575</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2599,37 +2599,37 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.09233202863200983</v>
+        <v>0.008287613941412596</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>urgency_pref</t>
+          <t>desktop_grid_pref</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13.44377621941306</v>
+        <v>13.59617637736529</v>
       </c>
       <c r="D33" t="n">
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09746555915938142</v>
+        <v>0.09291733321789566</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5708697036478054</v>
+        <v>0.4762013327417153</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1833287771969602</v>
+        <v>0.1742085186929457</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.7065257387806477</v>
+        <v>0.7269418893768508</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2666,37 +2666,37 @@
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.09746555915938142</v>
+        <v>0.09291733321789566</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Openness_Level</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>urgency_pref</t>
+          <t>product_desc_length</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13.43937531487906</v>
+        <v>13.05854568015153</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>0.09759978007500117</v>
+        <v>0.04211560054246764</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5135785999327165</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1832987678278216</v>
+        <v>0.1707294335040797</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2704,19 +2704,19 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.7239079153571463</v>
+        <v>0.762061183782854</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.09759978007500117</v>
+        <v>0.04211560054246764</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2748,22 +2748,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>13.10410015024543</v>
+        <v>12.97274309873333</v>
       </c>
       <c r="D35" t="n">
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01077818585613501</v>
+        <v>0.01140974677560341</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4419056201015353</v>
+        <v>0.4677996177997398</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1809979292025563</v>
+        <v>0.1701676110350818</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7734609471557843</v>
+        <v>0.7529034949121673</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.01077818585613501</v>
+        <v>0.01140974677560341</v>
       </c>
     </row>
     <row r="36">
@@ -2811,26 +2811,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>product_desc_length</t>
+          <t>mobile_review_display</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12.46883564401741</v>
+        <v>12.87108487837288</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>0.05229061052089522</v>
+        <v>0.01192317964216519</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4496070433508397</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1765561924998484</v>
+        <v>0.1694995580375933</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0.7501754525434632</v>
+        <v>0.7711007668807367</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2867,37 +2867,37 @@
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.05229061052089522</v>
+        <v>0.01192317964216519</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Openness_Level</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hero_banner_size</t>
+          <t>recommendation_type</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12.24912512714996</v>
+        <v>12.74073890201653</v>
       </c>
       <c r="D37" t="n">
         <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0566363742326912</v>
+        <v>0.0473428383179138</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6211380387310291</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5135785999327165</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1749937507966353</v>
+        <v>0.168639109742842</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.7269510006415666</v>
+        <v>0.7572744560321533</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0566363742326912</v>
+        <v>0.0473428383179138</v>
       </c>
     </row>
     <row r="38">
@@ -2949,22 +2949,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11.93080610517464</v>
+        <v>12.12651145964285</v>
       </c>
       <c r="D38" t="n">
         <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>0.06353035690835408</v>
+        <v>0.05920527162491043</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4496070433508397</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1727049948986323</v>
+        <v>0.164523876494273</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.740829219996215</v>
+        <v>0.7472907356683859</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3001,37 +3001,37 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.06353035690835408</v>
+        <v>0.05920527162491043</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mobile_navigation</t>
+          <t>desktop_quick_view</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11.60418948556712</v>
+        <v>11.99578986095121</v>
       </c>
       <c r="D39" t="n">
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>0.07140424468290275</v>
+        <v>0.06206279337045296</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.6361436320471427</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1703246127660879</v>
+        <v>0.1636347049189411</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0.7191621012651758</v>
+        <v>0.6742905825672968</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3068,37 +3068,37 @@
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0.07140424468290275</v>
+        <v>0.06206279337045296</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Agreeableness_Level</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>mobile_review_display</t>
+          <t>mobile_category_display</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11.47430384118304</v>
+        <v>11.70020776894192</v>
       </c>
       <c r="D40" t="n">
         <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.02172015497782318</v>
+        <v>0.0197255591239883</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7192283768587451</v>
+        <v>0.4043739620417602</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1693687090431925</v>
+        <v>0.161606111266038</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.668848294340231</v>
+        <v>0.7573388296353425</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3135,37 +3135,37 @@
         <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.02172015497782318</v>
+        <v>0.0197255591239883</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Agreeableness_Level</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>desktop_quick_view</t>
+          <t>mobile_navigation</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11.42221326826607</v>
+        <v>11.15364439421177</v>
       </c>
       <c r="D41" t="n">
         <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>0.07617164576328929</v>
+        <v>0.08374236488545971</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7192283768587451</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1689838251746752</v>
+        <v>0.1577863354845764</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6489406676885352</v>
+        <v>0.7257305983553333</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3202,37 +3202,37 @@
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0.07617164576328929</v>
+        <v>0.08374236488545971</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Openness_Level</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>font_style_pref</t>
+          <t>desktop_category_display</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11.33767608901562</v>
+        <v>10.87889431383801</v>
       </c>
       <c r="D42" t="n">
         <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.07848422212353164</v>
+        <v>0.0921922428414796</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5135785999327165</v>
+        <v>0.4762013327417153</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1683573289837394</v>
+        <v>0.1558308256932676</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.7099633355539084</v>
+        <v>0.7014943187126739</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.07848422212353164</v>
+        <v>0.0921922428414796</v>
       </c>
     </row>
     <row r="43">
@@ -3284,22 +3284,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10.76530026029114</v>
+        <v>10.74552473033666</v>
       </c>
       <c r="D43" t="n">
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>0.09590664672214096</v>
+        <v>0.09656696712661436</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5135785999327165</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H43" t="n">
-        <v>0.164052585016902</v>
+        <v>0.154872677619627</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6977876418547606</v>
+        <v>0.7170846983587206</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3336,37 +3336,37 @@
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0.09590664672214096</v>
+        <v>0.09656696712661436</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>Conscientiousness_Level</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>desktop_persistent_filters</t>
+          <t>mobile_category_display</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5.227393993591176</v>
+        <v>9.834181075946947</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>0.07326318869886991</v>
+        <v>0.04331545959948168</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.5709540419064413</v>
       </c>
       <c r="H44" t="n">
-        <v>0.161669322903128</v>
+        <v>0.1481597011488766</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3374,19 +3374,19 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0.7064831337951425</v>
+        <v>0.6792390903768705</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3403,37 +3403,37 @@
         <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.07326318869886991</v>
+        <v>0.04331545959948168</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Conscientiousness_Level</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mobile_category_display</t>
+          <t>mobile_whitespace</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9.909757842530952</v>
+        <v>9.778671590171463</v>
       </c>
       <c r="D45" t="n">
         <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>0.04197554673097541</v>
+        <v>0.04432561412731091</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H45" t="n">
-        <v>0.157398839278844</v>
+        <v>0.1477409623034418</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0.7175291579059003</v>
+        <v>0.7291182389879609</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0.04197554673097541</v>
+        <v>0.04432561412731091</v>
       </c>
     </row>
     <row r="46">
@@ -3481,26 +3481,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>mobile_filter_location</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9.114548333657801</v>
+        <v>9.161087482754875</v>
       </c>
       <c r="D46" t="n">
         <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>0.05829922747642777</v>
+        <v>0.05719678862795659</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4496070433508397</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1509515512810137</v>
+        <v>0.1429994964616733</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.7124864792419897</v>
+        <v>0.7178990775909611</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3537,37 +3537,37 @@
         <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.05829922747642777</v>
+        <v>0.05719678862795659</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>desktop_filter_location</t>
+          <t>mobile_info_density</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8.818633385094076</v>
+        <v>8.949865901211828</v>
       </c>
       <c r="D47" t="n">
         <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.06579615268548873</v>
+        <v>0.06236488381170928</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4496070433508397</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1484809195241435</v>
+        <v>0.141341357159808</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.7063887692035772</v>
+        <v>0.7103464673871202</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3604,37 +3604,37 @@
         <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.06579615268548873</v>
+        <v>0.06236488381170928</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>desktop_persistent_filters</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8.717019091514121</v>
+        <v>4.464545665170419</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.06857524433275533</v>
+        <v>0.0346052914835869</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H48" t="n">
-        <v>0.147622991870458</v>
+        <v>0.1411772199534915</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
       </c>
       <c r="L48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0.6886481980251703</v>
+        <v>0.7134892586633661</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3671,37 +3671,37 @@
         <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0.06857524433275533</v>
+        <v>0.0346052914835869</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>Conscientiousness_Level</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>mobile_whitespace</t>
+          <t>mobile_search_visibility</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8.294739366531338</v>
+        <v>8.570407151501566</v>
       </c>
       <c r="D49" t="n">
         <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08135899822583084</v>
+        <v>0.07278157564323007</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4584486025236872</v>
+        <v>0.5709540419064413</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1440029458598967</v>
+        <v>0.1383125920009826</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6919378315206305</v>
+        <v>0.6549643060288074</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3738,37 +3738,37 @@
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.08135899822583084</v>
+        <v>0.07278157564323007</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>desktop_persistent_filters</t>
+          <t>mobile_search_visibility</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.990493561045708</v>
+        <v>8.153991424098399</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>0.04575765883303096</v>
+        <v>0.08609740385555908</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1412532045839263</v>
+        <v>0.1349106137948581</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3776,19 +3776,19 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
       </c>
       <c r="L50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.673284109208215</v>
+        <v>0.6928936793247977</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.04575765883303096</v>
+        <v>0.08609740385555908</v>
       </c>
     </row>
     <row r="51">
@@ -3816,26 +3816,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>mobile_search_visibility</t>
+          <t>mobile_review_display</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7.820658223420017</v>
+        <v>7.860747163037939</v>
       </c>
       <c r="D51" t="n">
         <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.09837307471740275</v>
+        <v>0.09681446934641817</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.5709540419064413</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1398271989226346</v>
+        <v>0.1324624876400149</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6730659252886886</v>
+        <v>0.638216646146908</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3872,74 +3872,7 @@
         <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.09837307471740275</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Openness_Level</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>mobile_info_density</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>7.779608380710677</v>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.09999331646852108</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.6151665697823192</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.5135785999327165</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.1394597467077031</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>200</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52" t="b">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.662187329754381</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Exploratory Evidence</t>
-        </is>
-      </c>
-      <c r="P52" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="b">
-        <v>0</v>
-      </c>
-      <c r="R52" t="b">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0.09999331646852108</v>
+        <v>0.09681446934641817</v>
       </c>
     </row>
   </sheetData>
